--- a/data/trans_orig/IP1020-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1020-Estudios-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82027</t>
+          <t>82098</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173627</t>
+          <t>173618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>8340</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>9156</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14021</t>
+          <t>14359</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>407190</t>
+          <t>407747</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414635</t>
+          <t>414542</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>468360</t>
+          <t>467835</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>475177</t>
+          <t>475186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>879057</t>
+          <t>878719</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>888577</t>
+          <t>888419</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>592</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>169600</t>
+          <t>169196</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155137</t>
+          <t>155125</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>327292</t>
+          <t>327177</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>332205</t>
+          <t>331613</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>10688</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>11887</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18606</t>
+          <t>18192</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>670728</t>
+          <t>670333</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>678504</t>
+          <t>678439</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>709951</t>
+          <t>710087</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>718681</t>
+          <t>718741</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1384389</t>
+          <t>1384803</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1395713</t>
+          <t>1395687</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13245</t>
+          <t>12554</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85232</t>
+          <t>85681</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91154</t>
+          <t>91219</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74148</t>
+          <t>73492</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81506</t>
+          <t>81424</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>162180</t>
+          <t>162871</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171490</t>
+          <t>171420</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>8981</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22671</t>
+          <t>21662</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>432529</t>
+          <t>432632</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>443664</t>
+          <t>443618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>483877</t>
+          <t>483423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490946</t>
+          <t>490866</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>919432</t>
+          <t>920441</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>932465</t>
+          <t>932807</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>10743</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>12343</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153708</t>
+          <t>154597</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>163145</t>
+          <t>163038</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166977</t>
+          <t>167042</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>325153</t>
+          <t>324558</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>333940</t>
+          <t>333634</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>11700</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26476</t>
+          <t>25770</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17236</t>
+          <t>17513</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20544</t>
+          <t>21579</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39130</t>
+          <t>40147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>680452</t>
+          <t>681158</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>694716</t>
+          <t>695228</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>730265</t>
+          <t>729988</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>741446</t>
+          <t>741415</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1415299</t>
+          <t>1414282</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1433885</t>
+          <t>1432850</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63983</t>
+          <t>63690</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123059</t>
+          <t>123410</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13622</t>
+          <t>13496</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10837</t>
+          <t>10842</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8785</t>
+          <t>9078</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21674</t>
+          <t>21229</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>458668</t>
+          <t>458794</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>467934</t>
+          <t>467764</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>477898</t>
+          <t>477893</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>486026</t>
+          <t>486001</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>939351</t>
+          <t>939796</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952240</t>
+          <t>951947</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>10859</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12742</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>168334</t>
+          <t>168735</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177004</t>
+          <t>176636</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>185486</t>
+          <t>185066</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>347455</t>
+          <t>348116</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>356940</t>
+          <t>357061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>15234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7657</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19103</t>
+          <t>19954</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15338</t>
+          <t>15728</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30510</t>
+          <t>31162</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>688933</t>
+          <t>689137</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>698911</t>
+          <t>699025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>725741</t>
+          <t>724890</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>737586</t>
+          <t>737187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1418705</t>
+          <t>1418053</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1433877</t>
+          <t>1433487</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>560</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>999</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11816</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48966</t>
+          <t>49141</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54145</t>
+          <t>54118</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53821</t>
+          <t>52966</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61095</t>
+          <t>61005</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104866</t>
+          <t>105178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113906</t>
+          <t>114074</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22557</t>
+          <t>22357</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24163</t>
+          <t>25553</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21213</t>
+          <t>21802</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40804</t>
+          <t>40987</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>437137</t>
+          <t>437337</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>451156</t>
+          <t>451189</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>492456</t>
+          <t>491066</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>506302</t>
+          <t>506216</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>935509</t>
+          <t>935326</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>955100</t>
+          <t>954511</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11033</t>
+          <t>11415</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10280</t>
+          <t>10017</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17211</t>
+          <t>17298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>138518</t>
+          <t>138136</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146985</t>
+          <t>146738</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>173069</t>
+          <t>173332</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181582</t>
+          <t>181754</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>315689</t>
+          <t>315602</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>326564</t>
+          <t>326459</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15551</t>
+          <t>14732</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32197</t>
+          <t>31055</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17429</t>
+          <t>17113</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34768</t>
+          <t>34309</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36451</t>
+          <t>36811</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60662</t>
+          <t>59312</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>631726</t>
+          <t>632868</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>648372</t>
+          <t>649191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>727204</t>
+          <t>727663</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>744543</t>
+          <t>744859</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1365233</t>
+          <t>1366583</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1389444</t>
+          <t>1389084</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1020-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1020-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,107 +723,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4376</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1353</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4747</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4531</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1353</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4094</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>85492</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>82469</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>85492</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>82098</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,53%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>264</t>
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173618</t>
+          <t>173181</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4502</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9220</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4120</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1545</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8340</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1393</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8430</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4502</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9156</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14359</t>
+          <t>13993</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>472489</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>467771</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>475170</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,06%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>622</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>411967</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>407747</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>414542</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>407657</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>414694</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,01%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>472489</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>467835</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>475186</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,06%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>878719</t>
+          <t>879085</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>888419</t>
+          <t>888422</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3015</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1267</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4870</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4413</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3013</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157540</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>155123</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,09%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>172799</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>169196</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>169653</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,27%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,46%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>157540</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>155125</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>487</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>327177</t>
+          <t>327169</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>331613</t>
+          <t>331608</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6453</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3113</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11247</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5387</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2582</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10688</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2129</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10536</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6453</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3233</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11887</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18192</t>
+          <t>17940</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1075</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>715521</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>710727</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>718861</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1010</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>675634</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>670333</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>678439</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>670485</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>678892</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,21%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1075</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>715521</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>710087</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>718741</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1384803</t>
+          <t>1385055</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1395687</t>
+          <t>1395751</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4936</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2402</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10711</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,82%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2658</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6208</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6344</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,89%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4936</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2113</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10045</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12554</t>
+          <t>12967</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>78601</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>72826</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>81135</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,09%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,18%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>89231</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>85681</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>91219</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>85545</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>91209</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,11%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,24%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>78601</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>73492</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>81424</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,09%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>162871</t>
+          <t>162458</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171420</t>
+          <t>171513</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4249</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9336</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>10330</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6082</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17068</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5970</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16200</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4249</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1538</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8981</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21662</t>
+          <t>21378</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>488155</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>483068</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>490859</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,1%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>636</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>439370</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>432632</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>443618</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>433500</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>443730</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,7%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>699</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>488155</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>483423</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>490866</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>920441</t>
+          <t>920725</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>932807</t>
+          <t>933272</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3921</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5290</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2302</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10743</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2228</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10487</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,2%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4519</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12343</t>
+          <t>11954</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>170273</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>167640</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>160050</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>154597</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>163038</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>154853</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>163112</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,8%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,5%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>170273</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>167042</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324558</t>
+          <t>324947</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>333634</t>
+          <t>333878</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10473</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5902</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16615</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>18278</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11700</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>25770</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>12126</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>26014</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,59%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10473</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6086</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>17513</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21579</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40147</t>
+          <t>38023</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>737028</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>730886</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>741599</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>992</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>688650</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>681158</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>695228</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>680914</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>694802</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,41%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>737028</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>729988</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>741415</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1414282</t>
+          <t>1416406</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1432850</t>
+          <t>1433421</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,92 +3929,92 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4131</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1327</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4924</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>7,18%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4042,74 +4042,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67287</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>64483</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>67287</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>63690</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>92,82%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>186</t>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123410</t>
+          <t>123416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6063</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3341</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11434</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>8041</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4526</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13496</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4642</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14239</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,7%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6063</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2734</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10842</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9078</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21229</t>
+          <t>20612</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>482672</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>477301</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>485394</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,76%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,66%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,32%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>701</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>464249</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>458794</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>467764</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>458051</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>467648</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,3%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>482672</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>477893</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>486001</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>939796</t>
+          <t>940413</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>951947</t>
+          <t>952064</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5315</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2149</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10273</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1231</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3968</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4341</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5315</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2429</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10859</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>11799</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -4728,74 +4728,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>182180</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>177222</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>185346</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,52%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,85%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>171472</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>168735</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>168362</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,29%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,49%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>182180</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>176636</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>185066</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,21%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,7%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>520</t>
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>348116</t>
+          <t>348398</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>357061</t>
+          <t>357101</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12706</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7671</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20758</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9273</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5346</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15234</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15348</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12706</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7657</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>19954</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>15747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31162</t>
+          <t>30705</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>732138</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>724086</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>737173</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1046</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>695098</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>689137</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>699025</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>689023</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>699086</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,68%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>732138</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>724890</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>737187</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,29%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1418053</t>
+          <t>1418510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1433487</t>
+          <t>1433468</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>963</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9038</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>11564</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52992</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47881</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>55769</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,41%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>84,4%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>52501</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49141</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54118</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,87%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,98%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58291</t>
+          <t>44555</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52966</t>
+          <t>41666</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61005</t>
+          <t>46194</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>110792</t>
+          <t>97547</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105178</t>
+          <t>91926</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>114074</t>
+          <t>100990</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15170</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9362</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22452</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>14131</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8505</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>22357</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16215</t>
+          <t>14565</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25553</t>
+          <t>22576</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>30346</t>
+          <t>29736</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21802</t>
+          <t>21266</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40987</t>
+          <t>38871</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>460508</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>453226</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>466316</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,81%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>623</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>445563</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>437337</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>451189</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>96,93%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,15%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>500404</t>
+          <t>417037</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>491066</t>
+          <t>409026</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>506216</t>
+          <t>423017</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>945967</t>
+          <t>877544</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>935326</t>
+          <t>868409</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>954511</t>
+          <t>886014</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4976</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1911</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10382</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6023</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2813</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11415</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10017</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>11289</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17298</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>163443</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>158037</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166508</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,05%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,84%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>143528</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>138136</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>146738</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>95,97%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,37%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,12%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>178506</t>
+          <t>143663</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>173332</t>
+          <t>138075</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181754</t>
+          <t>147005</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>322034</t>
+          <t>307106</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>315602</t>
+          <t>299724</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>326459</t>
+          <t>311897</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23886</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16439</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33216</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>22331</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14732</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>31055</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24771</t>
+          <t>23082</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17113</t>
+          <t>15931</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34309</t>
+          <t>33371</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>47102</t>
+          <t>46968</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36811</t>
+          <t>36206</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59312</t>
+          <t>59389</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>676943</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>667613</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>684390</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,26%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>909</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>641592</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>632868</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>649191</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>96,64%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>943</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>737201</t>
+          <t>605254</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>727663</t>
+          <t>594965</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>744859</t>
+          <t>612405</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1378793</t>
+          <t>1282197</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1366583</t>
+          <t>1269776</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1389084</t>
+          <t>1292959</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1425895</t>
+          <t>1329165</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1425895</t>
+          <t>1329165</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1425895</t>
+          <t>1329165</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
